--- a/Raw Data/Projects_KV.xlsx
+++ b/Raw Data/Projects_KV.xlsx
@@ -1,32 +1,98 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5546F5AB-F01E-4F71-98FF-FC12BB561820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>TA413</t>
+  </si>
+  <si>
+    <t>TA419</t>
+  </si>
+  <si>
+    <t>TB408</t>
+  </si>
+  <si>
+    <t>TA325</t>
+  </si>
+  <si>
+    <t>TA416</t>
+  </si>
+  <si>
+    <t>TA418</t>
+  </si>
+  <si>
+    <t>TA421</t>
+  </si>
+  <si>
+    <t>TA504</t>
+  </si>
+  <si>
+    <t>TA505</t>
+  </si>
+  <si>
+    <t>TA506</t>
+  </si>
+  <si>
+    <t>TA509</t>
+  </si>
+  <si>
+    <t>Voltage</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +103,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +111,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +417,107 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>765</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Raw Data/Projects_KV.xlsx
+++ b/Raw Data/Projects_KV.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5546F5AB-F01E-4F71-98FF-FC12BB561820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9054DEAF-3EA8-4F11-AF1C-3B5D722B8F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$H$1:$H$17</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Project</t>
   </si>
@@ -71,10 +74,25 @@
     <t>TA506</t>
   </si>
   <si>
-    <t>TA509</t>
-  </si>
-  <si>
     <t>Voltage</t>
+  </si>
+  <si>
+    <t>TA512</t>
+  </si>
+  <si>
+    <t>TB401</t>
+  </si>
+  <si>
+    <t>TB507</t>
+  </si>
+  <si>
+    <t>TA414</t>
+  </si>
+  <si>
+    <t>TA513</t>
+  </si>
+  <si>
+    <t>TB605</t>
   </si>
 </sst>
 </file>
@@ -93,6 +111,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -418,66 +437,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B3">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
       <c r="B7">
         <v>765</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -485,7 +506,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -493,7 +514,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -501,7 +522,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -509,12 +530,52 @@
         <v>765</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>765</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>400</v>
       </c>
     </row>
   </sheetData>

--- a/Raw Data/Projects_KV.xlsx
+++ b/Raw Data/Projects_KV.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9054DEAF-3EA8-4F11-AF1C-3B5D722B8F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B5637E-0DC8-4148-9864-A7B9BF085760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,12 +114,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -149,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -157,6 +163,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,10 +444,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -450,71 +457,95 @@
       <c r="D1" s="2"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
         <v>765</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F2" s="3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
         <v>765</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F3" s="3">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4">
         <v>765</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F4" s="3">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
         <v>765</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F5" s="3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6">
         <v>765</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F6">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>2</v>
       </c>
       <c r="B7">
         <v>765</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F7" s="3">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
         <v>765</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F8">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
         <v>400</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F9" s="3">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -522,7 +553,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -530,7 +561,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -538,7 +569,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -546,7 +577,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -554,7 +585,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -562,7 +593,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>

--- a/Raw Data/Projects_KV.xlsx
+++ b/Raw Data/Projects_KV.xlsx
@@ -1,131 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB0AB69-17C9-42C9-96B9-BEF26F6757CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>Voltage</t>
-  </si>
-  <si>
-    <t>TA325</t>
-  </si>
-  <si>
-    <t>TA413</t>
-  </si>
-  <si>
-    <t>TA414</t>
-  </si>
-  <si>
-    <t>TA416</t>
-  </si>
-  <si>
-    <t>TA418</t>
-  </si>
-  <si>
-    <t>TA419</t>
-  </si>
-  <si>
-    <t>TA421</t>
-  </si>
-  <si>
-    <t>TA504</t>
-  </si>
-  <si>
-    <t>TA505</t>
-  </si>
-  <si>
-    <t>TA506</t>
-  </si>
-  <si>
-    <t>TA512</t>
-  </si>
-  <si>
-    <t>TA513</t>
-  </si>
-  <si>
-    <t>TA 601</t>
-  </si>
-  <si>
-    <t>765</t>
-  </si>
-  <si>
-    <t>TB401</t>
-  </si>
-  <si>
-    <t>TB408</t>
-  </si>
-  <si>
-    <t>TB 501</t>
-  </si>
-  <si>
-    <t>132/220</t>
-  </si>
-  <si>
-    <t>TB507</t>
-  </si>
-  <si>
-    <t>TB605</t>
-  </si>
-  <si>
-    <t>TA 509</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -159,24 +67,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -464,172 +431,236 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Voltage</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TA325</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TA413</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TA414</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TA416</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TA418</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TA419</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TA421</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TA504</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TA505</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TA506</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TA512</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TA513</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TA 601</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TB401</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TB408</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TB 501</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>132/220</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TB507</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TB605</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>400</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" t="s">
-        <v>15</v>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TA 509</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TB412</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>220/400</t>
+        </is>
       </c>
     </row>
   </sheetData>
